--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -173,7 +173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,12 +183,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,17 +233,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,76 +46,34 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>В2071ХК</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>В8987ВР</t>
   </si>
   <si>
     <t>В7243ВР</t>
   </si>
   <si>
-    <t>В8987ВР</t>
-  </si>
-  <si>
-    <t>78970155027720527</t>
+    <t>В2525КН</t>
+  </si>
+  <si>
+    <t>78970155027720501</t>
   </si>
   <si>
     <t>78970155027720519</t>
   </si>
   <si>
-    <t>78970155027720501</t>
+    <t>78970155027720493</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:06:00</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>10:19:00</t>
-  </si>
-  <si>
-    <t>10:22:00</t>
-  </si>
-  <si>
-    <t>10:48:00</t>
-  </si>
-  <si>
-    <t>3232057235 3232057235</t>
-  </si>
-  <si>
-    <t>3232159931 3232159931</t>
-  </si>
-  <si>
-    <t>3232243358 3232243358</t>
-  </si>
-  <si>
-    <t>3232517578 3232517578</t>
-  </si>
-  <si>
-    <t>3232574532 3232574532</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -538,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +502,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,327 +543,343 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>15.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>15.7</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>17.59</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H3">
+        <v>13.02</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="J3">
+        <v>13.19</v>
+      </c>
+      <c r="K3">
+        <v>89505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>36.51</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H4">
+        <v>56.23</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J4">
+        <v>57.32</v>
+      </c>
+      <c r="K4">
+        <v>81018</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>46.6</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H5">
+        <v>71.3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J5">
+        <v>72.7</v>
+      </c>
+      <c r="K5">
+        <v>334685</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>23.4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6">
+        <v>16.61</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J6">
+        <v>16.85</v>
+      </c>
+      <c r="K6">
+        <v>89693</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>36.64</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H7">
+        <v>56.06</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J7">
+        <v>57.16</v>
+      </c>
+      <c r="K7">
+        <v>81380</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F8">
+        <v>24.07</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="H8">
+        <v>16.13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J8">
+        <v>16.37</v>
+      </c>
+      <c r="K8">
+        <v>89913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>25.72</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>39.09</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>39.87</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="7">
+        <v>129.75</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.5336</v>
+      </c>
+      <c r="E13" s="7">
+        <v>198.99</v>
+      </c>
+      <c r="F13" s="7">
+        <v>202.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="7">
+        <v>65.06</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.7034</v>
+      </c>
+      <c r="E14" s="7">
+        <v>45.76</v>
+      </c>
+      <c r="F14" s="7">
+        <v>46.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M2">
-        <v>5745</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>33.12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>51</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>52</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>22.57</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>0.78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.6</v>
-      </c>
-      <c r="J4">
-        <v>0.79</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.83</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>26.82</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>41.3</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>42.11</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>6054</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>25.45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>0.76</v>
-      </c>
-      <c r="I6" s="1">
-        <v>19.34</v>
-      </c>
-      <c r="J6">
-        <v>0.77</v>
-      </c>
-      <c r="K6" s="1">
-        <v>19.6</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7">
-        <v>85.66</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.5339</v>
-      </c>
-      <c r="E11" s="7">
-        <v>131.39</v>
-      </c>
-      <c r="F11" s="7">
-        <v>133.98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="7">
-        <v>48.02</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.7693</v>
-      </c>
-      <c r="E12" s="7">
-        <v>36.94</v>
-      </c>
-      <c r="F12" s="7">
-        <v>37.43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="10">
-        <v>133.68</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>168.33</v>
-      </c>
-      <c r="F13" s="10">
-        <v>171.41</v>
+      <c r="B15" s="10">
+        <v>194.81</v>
+      </c>
+      <c r="C15" s="10">
+        <v>7</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>244.75</v>
+      </c>
+      <c r="F15" s="10">
+        <v>249.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -74,6 +80,27 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>14:08</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -493,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,10 +533,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,22 +572,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -575,25 +610,31 @@
       <c r="J2">
         <v>15.7</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>213936</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46175</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>17.59</v>
@@ -610,25 +651,31 @@
       <c r="J3">
         <v>13.19</v>
       </c>
-      <c r="K3">
-        <v>89505</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>180188</v>
+      </c>
+      <c r="M3">
+        <v>213942</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46175</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>36.51</v>
@@ -645,25 +692,31 @@
       <c r="J4">
         <v>57.32</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>81018</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>214016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46181</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>46.6</v>
@@ -680,25 +733,31 @@
       <c r="J5">
         <v>72.7</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
         <v>334685</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>216299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46181</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>23.4</v>
@@ -715,25 +774,31 @@
       <c r="J6">
         <v>16.85</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
         <v>89693</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>216440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46182</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>36.64</v>
@@ -750,25 +815,31 @@
       <c r="J7">
         <v>57.16</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
         <v>81380</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>216751</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46185</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>24.07</v>
@@ -785,13 +856,19 @@
       <c r="J8">
         <v>16.37</v>
       </c>
-      <c r="K8">
-        <v>89913</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>82839</v>
+      </c>
+      <c r="M8">
+        <v>218233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -799,18 +876,18 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>7</v>
@@ -819,9 +896,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="7">
         <v>129.75</v>
@@ -839,9 +916,9 @@
         <v>202.88</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="7">
         <v>65.06</v>
@@ -859,9 +936,9 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B15" s="10">
         <v>194.81</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -49,22 +49,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Порт</t>
   </si>
   <si>
+    <t>В2071ХК</t>
+  </si>
+  <si>
     <t>В8987ВР</t>
   </si>
   <si>
     <t>В7243ВР</t>
   </si>
   <si>
-    <t>В2525КН</t>
+    <t>78970155027720527</t>
   </si>
   <si>
     <t>78970155027720501</t>
@@ -73,34 +70,22 @@
     <t>78970155027720519</t>
   </si>
   <si>
-    <t>78970155027720493</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>11:54</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>12:01</t>
-  </si>
-  <si>
-    <t>14:08</t>
+    <t>2026-06-16 11:38:09</t>
+  </si>
+  <si>
+    <t>2026-06-18 11:50:12</t>
+  </si>
+  <si>
+    <t>2026-06-18 14:21:14</t>
+  </si>
+  <si>
+    <t>2026-06-23 13:30:15</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -520,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,12 +518,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,391 +555,238 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>44.55</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H2">
+        <v>68.16</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>69.5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>21.02</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>13.66</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>13.87</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>15.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>15.7</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>38.06</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>57.85</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J4">
+        <v>58.99</v>
+      </c>
+      <c r="K4" t="s">
         <v>22</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>213936</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46196</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>17.59</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="H3">
-        <v>13.02</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="J3">
-        <v>13.19</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>21.67</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>14.09</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>14.3</v>
+      </c>
+      <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="L3">
-        <v>180188</v>
-      </c>
-      <c r="M3">
-        <v>213942</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>36.51</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H4">
-        <v>56.23</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J4">
-        <v>57.32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>81018</v>
-      </c>
-      <c r="M4">
-        <v>214016</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B10" s="7">
+        <v>82.61</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.5254</v>
+      </c>
+      <c r="E10" s="7">
+        <v>126.01</v>
+      </c>
+      <c r="F10" s="7">
+        <v>128.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>46.6</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H5">
-        <v>71.3</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J5">
-        <v>72.7</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>334685</v>
-      </c>
-      <c r="M5">
-        <v>216299</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>23.4</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H6">
-        <v>16.61</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J6">
-        <v>16.85</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>89693</v>
-      </c>
-      <c r="M6">
-        <v>216440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>36.64</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H7">
-        <v>56.06</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J7">
-        <v>57.16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>81380</v>
-      </c>
-      <c r="M7">
-        <v>216751</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8">
-        <v>24.07</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="H8">
-        <v>16.13</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="J8">
-        <v>16.37</v>
-      </c>
-      <c r="K8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>82839</v>
-      </c>
-      <c r="M8">
-        <v>218233</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="7">
+        <v>42.69</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E11" s="7">
+        <v>27.75</v>
+      </c>
+      <c r="F11" s="7">
+        <v>28.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="7">
-        <v>129.75</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B12" s="10">
+        <v>125.3</v>
+      </c>
+      <c r="C12" s="10">
         <v>4</v>
       </c>
-      <c r="D13" s="8">
-        <v>1.5336</v>
-      </c>
-      <c r="E13" s="7">
-        <v>198.99</v>
-      </c>
-      <c r="F13" s="7">
-        <v>202.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="7">
-        <v>65.06</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.7034</v>
-      </c>
-      <c r="E14" s="7">
-        <v>45.76</v>
-      </c>
-      <c r="F14" s="7">
-        <v>46.41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="10">
-        <v>194.81</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10">
-        <v>244.75</v>
-      </c>
-      <c r="F15" s="10">
-        <v>249.29</v>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>153.76</v>
+      </c>
+      <c r="F12" s="10">
+        <v>156.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="47">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В2071ХК</t>
@@ -61,6 +73,9 @@
     <t>В7243ВР</t>
   </si>
   <si>
+    <t>В2525КН</t>
+  </si>
+  <si>
     <t>78970155027720527</t>
   </si>
   <si>
@@ -70,22 +85,58 @@
     <t>78970155027720519</t>
   </si>
   <si>
+    <t>78970155027720493</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 11:38:09</t>
-  </si>
-  <si>
-    <t>2026-06-18 11:50:12</t>
-  </si>
-  <si>
-    <t>2026-06-18 14:21:14</t>
-  </si>
-  <si>
-    <t>2026-06-23 13:30:15</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:38:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>13:33:00</t>
+  </si>
+  <si>
+    <t>14:23:00</t>
+  </si>
+  <si>
+    <t>11:05:00</t>
+  </si>
+  <si>
+    <t>3233404371 3233404371</t>
+  </si>
+  <si>
+    <t>3233533209 3233533209</t>
+  </si>
+  <si>
+    <t>3233534398 3233534398</t>
+  </si>
+  <si>
+    <t>3233770151 3233770151</t>
+  </si>
+  <si>
+    <t>3234037787 3234037787</t>
+  </si>
+  <si>
+    <t>3234064312 3234064312</t>
+  </si>
+  <si>
+    <t>3234094421 3234094421</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -505,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,14 +565,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,238 +609,415 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>44.55</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>68.16</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>69.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>6587</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46191</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>21.02</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
         <v>0.65</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>13.66</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>13.87</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
+        <v>90124</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>38.06</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
         <v>1.52</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>57.85</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.55</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>58.99</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
+        <v>81739</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46196</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>21.67</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
         <v>0.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>14.09</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.66</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>14.3</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>90315</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>24.48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>0.65</v>
+      </c>
+      <c r="I6" s="1">
+        <v>15.91</v>
+      </c>
+      <c r="J6">
+        <v>0.66</v>
+      </c>
+      <c r="K6" s="1">
+        <v>16.16</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>90526</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s">
+      <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="5" t="s">
+      <c r="F7">
+        <v>52.42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>1.47</v>
+      </c>
+      <c r="I7" s="1">
+        <v>77.06</v>
+      </c>
+      <c r="J7">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>78.63</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>335017</v>
+      </c>
+      <c r="N7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>47.92</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>1.47</v>
+      </c>
+      <c r="I8" s="1">
+        <v>70.44</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>71.88</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8">
+        <v>7137</v>
+      </c>
+      <c r="N8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7">
+        <v>182.95</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.495</v>
+      </c>
+      <c r="E13" s="7">
+        <v>273.51</v>
+      </c>
+      <c r="F13" s="7">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="B14" s="7">
+        <v>67.17</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E14" s="7">
+        <v>43.66</v>
+      </c>
+      <c r="F14" s="7">
+        <v>44.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="10">
+        <v>250.12</v>
+      </c>
+      <c r="C15" s="10">
         <v>7</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="7">
-        <v>82.61</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.5254</v>
-      </c>
-      <c r="E10" s="7">
-        <v>126.01</v>
-      </c>
-      <c r="F10" s="7">
-        <v>128.49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="7">
-        <v>42.69</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="E11" s="7">
-        <v>27.75</v>
-      </c>
-      <c r="F11" s="7">
-        <v>28.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="10">
-        <v>125.3</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>153.76</v>
-      </c>
-      <c r="F12" s="10">
-        <v>156.66</v>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>317.17</v>
+      </c>
+      <c r="F15" s="10">
+        <v>323.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В2071ХК</t>
@@ -94,49 +91,25 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:38:00</t>
-  </si>
-  <si>
-    <t>11:50:00</t>
-  </si>
-  <si>
-    <t>14:20:00</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>13:33:00</t>
-  </si>
-  <si>
-    <t>14:23:00</t>
-  </si>
-  <si>
-    <t>11:05:00</t>
-  </si>
-  <si>
-    <t>3233404371 3233404371</t>
-  </si>
-  <si>
-    <t>3233533209 3233533209</t>
-  </si>
-  <si>
-    <t>3233534398 3233534398</t>
-  </si>
-  <si>
-    <t>3233770151 3233770151</t>
-  </si>
-  <si>
-    <t>3234037787 3234037787</t>
-  </si>
-  <si>
-    <t>3234064312 3234064312</t>
-  </si>
-  <si>
-    <t>3234094421 3234094421</t>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>11:05</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -556,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -565,17 +538,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,321 +587,297 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>44.55</v>
       </c>
-      <c r="G2" t="s">
-        <v>26</v>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>68.16</v>
       </c>
       <c r="I2" s="1">
-        <v>68.16</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
         <v>69.5</v>
       </c>
-      <c r="L2" t="s">
-        <v>27</v>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2">
+        <v>6587</v>
       </c>
       <c r="M2">
-        <v>6587</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>219798</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46191</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>21.02</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>13.66</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>13.87</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="H3">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>13.66</v>
-      </c>
-      <c r="J3">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>13.87</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
+      <c r="L3">
+        <v>90124</v>
       </c>
       <c r="M3">
-        <v>90124</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>220681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>38.06</v>
       </c>
-      <c r="G4" t="s">
-        <v>26</v>
+      <c r="G4" s="1">
+        <v>1.52</v>
       </c>
       <c r="H4">
-        <v>1.52</v>
+        <v>57.85</v>
       </c>
       <c r="I4" s="1">
-        <v>57.85</v>
+        <v>1.55</v>
       </c>
       <c r="J4">
-        <v>1.55</v>
-      </c>
-      <c r="K4" s="1">
         <v>58.99</v>
       </c>
-      <c r="L4" t="s">
-        <v>29</v>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4">
+        <v>81739</v>
       </c>
       <c r="M4">
-        <v>81739</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>220789</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46196</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>21.67</v>
       </c>
-      <c r="G5" t="s">
-        <v>26</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>14.09</v>
       </c>
       <c r="I5" s="1">
-        <v>14.09</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>14.3</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>90315</v>
       </c>
       <c r="M5">
-        <v>90315</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>222994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46202</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>24.48</v>
       </c>
-      <c r="G6" t="s">
-        <v>26</v>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6">
-        <v>0.65</v>
+        <v>15.91</v>
       </c>
       <c r="I6" s="1">
-        <v>15.91</v>
+        <v>0.66</v>
       </c>
       <c r="J6">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
         <v>16.16</v>
       </c>
-      <c r="L6" t="s">
-        <v>31</v>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>49740</v>
       </c>
       <c r="M6">
-        <v>90526</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>146487</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46202</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
         <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
       </c>
       <c r="F7">
         <v>52.42</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
+      <c r="G7" s="1">
+        <v>1.47</v>
       </c>
       <c r="H7">
-        <v>1.47</v>
+        <v>77.06</v>
       </c>
       <c r="I7" s="1">
-        <v>77.06</v>
+        <v>1.5</v>
       </c>
       <c r="J7">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="1">
         <v>78.63</v>
       </c>
-      <c r="L7" t="s">
-        <v>32</v>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>335017</v>
       </c>
       <c r="M7">
-        <v>335017</v>
-      </c>
-      <c r="N7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>225545</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46203</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>47.92</v>
       </c>
-      <c r="G8" t="s">
-        <v>26</v>
+      <c r="G8" s="1">
+        <v>1.47</v>
       </c>
       <c r="H8">
-        <v>1.47</v>
+        <v>70.44</v>
       </c>
       <c r="I8" s="1">
-        <v>70.44</v>
+        <v>1.5</v>
       </c>
       <c r="J8">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="1">
         <v>71.88</v>
       </c>
-      <c r="L8" t="s">
-        <v>33</v>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8">
+        <v>7137</v>
       </c>
       <c r="M8">
-        <v>7137</v>
-      </c>
-      <c r="N8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>225902</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -937,29 +885,29 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="7">
         <v>182.95</v>
@@ -977,9 +925,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="7">
         <v>67.17</v>
@@ -997,9 +945,9 @@
         <v>44.33</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B15" s="10">
         <v>250.12</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,37 +55,103 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>В8987ВР</t>
+  </si>
+  <si>
+    <t>В2071ХК</t>
   </si>
   <si>
     <t>В7243ВР</t>
   </si>
   <si>
-    <t>В8987ВР</t>
+    <t>В2525КН</t>
+  </si>
+  <si>
+    <t>78970155027720501</t>
+  </si>
+  <si>
+    <t>78970155027720527</t>
   </si>
   <si>
     <t>78970155027720519</t>
   </si>
   <si>
-    <t>78970155027720501</t>
+    <t>78970155027720493</t>
+  </si>
+  <si>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>2026-07-01 15:03:07</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:57:24</t>
-  </si>
-  <si>
-    <t>2026-07-10 12:44:08</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:41:48</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:54:00</t>
+  </si>
+  <si>
+    <t>12:36:00</t>
+  </si>
+  <si>
+    <t>11:16:00</t>
+  </si>
+  <si>
+    <t>14:31:00</t>
+  </si>
+  <si>
+    <t>16:24:00</t>
+  </si>
+  <si>
+    <t>11:33:00</t>
+  </si>
+  <si>
+    <t>14:54:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>11:59:00</t>
+  </si>
+  <si>
+    <t>3234890652 3234890652</t>
+  </si>
+  <si>
+    <t>3234892217 3234892217</t>
+  </si>
+  <si>
+    <t>3234926984 3234926984</t>
+  </si>
+  <si>
+    <t>3234945778 3234945778</t>
+  </si>
+  <si>
+    <t>3235150688 3235150688</t>
+  </si>
+  <si>
+    <t>3235196002 3235196002</t>
+  </si>
+  <si>
+    <t>3235303027 3235303027</t>
+  </si>
+  <si>
+    <t>3235486417 3235486417</t>
+  </si>
+  <si>
+    <t>3235486594 3235486594</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -502,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,15 +580,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -556,250 +627,500 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>24.48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15.18</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15.42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>91080</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>48.31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>1.47</v>
+      </c>
+      <c r="I3" s="1">
+        <v>71.02</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>7692</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>40.07</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>1.48</v>
+      </c>
+      <c r="I4" s="1">
+        <v>59.3</v>
+      </c>
+      <c r="J4">
+        <v>1.51</v>
+      </c>
+      <c r="K4" s="1">
+        <v>60.51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>82854</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>38.58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>1.48</v>
+      </c>
+      <c r="I5" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="J5">
+        <v>1.51</v>
+      </c>
+      <c r="K5" s="1">
+        <v>58.26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>335331</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>6.47</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J6">
+        <v>1.53</v>
+      </c>
+      <c r="K6" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
+        <v>335372</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>38.48</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>56.57</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>57.72</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>18.45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>0.63</v>
+      </c>
+      <c r="I7" s="1">
+        <v>11.62</v>
+      </c>
+      <c r="J7">
+        <v>0.64</v>
+      </c>
+      <c r="K7" s="1">
+        <v>11.81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>91236</v>
+      </c>
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
-        <v>82096</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>38.66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8">
+        <v>1.51</v>
+      </c>
+      <c r="I8" s="1">
+        <v>58.38</v>
+      </c>
+      <c r="J8">
+        <v>1.54</v>
+      </c>
+      <c r="K8" s="1">
+        <v>59.54</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>83225</v>
+      </c>
+      <c r="N8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>19.13</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H3">
-        <v>11.86</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>1.53</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="J9">
+        <v>1.56</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>91449</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>23.52</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10">
         <v>0.63</v>
       </c>
-      <c r="J3">
-        <v>12.05</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>90687</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>43.23</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H4">
-        <v>63.12</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J4">
-        <v>64.41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4">
-        <v>82483</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>22.4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H5">
-        <v>13.89</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J5">
-        <v>14.11</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5">
-        <v>90859</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="I10" s="1">
+        <v>14.82</v>
+      </c>
+      <c r="J10">
+        <v>0.64</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15.05</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>91449</v>
+      </c>
+      <c r="N10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="7">
+        <v>182.09</v>
+      </c>
+      <c r="C15" s="7">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.4872</v>
+      </c>
+      <c r="E15" s="7">
+        <v>270.8</v>
+      </c>
+      <c r="F15" s="7">
+        <v>276.27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="B16" s="7">
+        <v>66.45</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.6263</v>
+      </c>
+      <c r="E16" s="7">
+        <v>41.62</v>
+      </c>
+      <c r="F16" s="7">
+        <v>42.28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="10">
+        <v>248.54</v>
+      </c>
+      <c r="C17" s="10">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="7">
-        <v>81.70999999999999</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.4648</v>
-      </c>
-      <c r="E10" s="7">
-        <v>119.69</v>
-      </c>
-      <c r="F10" s="7">
-        <v>122.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7">
-        <v>41.53</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="7">
-        <v>25.75</v>
-      </c>
-      <c r="F11" s="7">
-        <v>26.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10">
-        <v>123.24</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>145.44</v>
-      </c>
-      <c r="F12" s="10">
-        <v>148.29</v>
+      <c r="D17" s="8"/>
+      <c r="E17" s="10">
+        <v>312.42</v>
+      </c>
+      <c r="F17" s="10">
+        <v>318.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -179,7 +179,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1071,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>1.4872</v>
+        <v>1.487177</v>
       </c>
       <c r="E15" s="7">
         <v>270.8</v>
@@ -1091,7 +1091,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>0.6263</v>
+        <v>0.626336</v>
       </c>
       <c r="E16" s="7">
         <v>41.62</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -571,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -584,13 +587,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -633,406 +636,436 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>24.48</v>
+        <v>24.476</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
-        <v>15.18</v>
-      </c>
       <c r="J2">
+        <v>15.17512</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>15.42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>15.41988</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2">
         <v>91080</v>
       </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>48.31</v>
+        <v>48.313</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3">
+        <v>1.369</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.47</v>
       </c>
-      <c r="I3" s="1">
-        <v>71.02</v>
-      </c>
       <c r="J3">
+        <v>71.02011</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.5</v>
       </c>
-      <c r="K3" s="1">
-        <v>72.45999999999999</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>72.4695</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3">
         <v>7692</v>
       </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>40.07</v>
+        <v>40.073</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
+        <v>1.369</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.48</v>
       </c>
-      <c r="I4" s="1">
-        <v>59.3</v>
-      </c>
       <c r="J4">
+        <v>59.30804</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.51</v>
       </c>
-      <c r="K4" s="1">
-        <v>60.51</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>60.51023</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
         <v>82854</v>
       </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>38.58</v>
+        <v>38.583</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5">
+        <v>1.369</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.48</v>
       </c>
-      <c r="I5" s="1">
-        <v>57.1</v>
-      </c>
       <c r="J5">
+        <v>57.10284</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.51</v>
       </c>
-      <c r="K5" s="1">
-        <v>58.26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>58.26033</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5">
         <v>335331</v>
       </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>6.47</v>
+        <v>6.471</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6">
+        <v>1.389</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.5</v>
       </c>
-      <c r="I6" s="1">
-        <v>9.699999999999999</v>
-      </c>
       <c r="J6">
+        <v>9.7065</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.53</v>
       </c>
-      <c r="K6" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>9.90063</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6">
         <v>335372</v>
       </c>
-      <c r="N6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>18.45</v>
+        <v>18.453</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>0.63</v>
       </c>
-      <c r="I7" s="1">
-        <v>11.62</v>
-      </c>
       <c r="J7">
+        <v>11.62539</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.64</v>
       </c>
-      <c r="K7" s="1">
-        <v>11.81</v>
-      </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>11.80992</v>
+      </c>
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7">
         <v>91236</v>
       </c>
-      <c r="N7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46227</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>38.66</v>
+        <v>38.662</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
+        <v>1.401</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.51</v>
       </c>
-      <c r="I8" s="1">
-        <v>58.38</v>
-      </c>
       <c r="J8">
+        <v>58.37962</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.54</v>
       </c>
-      <c r="K8" s="1">
-        <v>59.54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>59.53948</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8">
         <v>83225</v>
       </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46231</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9">
+        <v>1.441</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.53</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>15.3</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1.56</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>15.6</v>
       </c>
-      <c r="L9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9">
         <v>91449</v>
       </c>
-      <c r="N9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46231</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>23.52</v>
+        <v>23.516</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
         <v>0.63</v>
       </c>
-      <c r="I10" s="1">
-        <v>14.82</v>
-      </c>
       <c r="J10">
+        <v>14.81508</v>
+      </c>
+      <c r="K10" s="1">
         <v>0.64</v>
       </c>
-      <c r="K10" s="1">
-        <v>15.05</v>
-      </c>
-      <c r="L10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>15.05024</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10">
         <v>91449</v>
       </c>
-      <c r="N10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1040,58 +1073,58 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="7">
-        <v>182.09</v>
+        <v>182.102</v>
       </c>
       <c r="C15" s="7">
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>1.487177</v>
+        <v>1.487173</v>
       </c>
       <c r="E15" s="7">
-        <v>270.8</v>
+        <v>270.82</v>
       </c>
       <c r="F15" s="7">
-        <v>276.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>276.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="7">
-        <v>66.45</v>
+        <v>66.44499999999999</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>0.626336</v>
+        <v>0.626316</v>
       </c>
       <c r="E16" s="7">
         <v>41.62</v>
@@ -1102,20 +1135,20 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="10">
-        <v>248.54</v>
+        <v>248.547</v>
       </c>
       <c r="C17" s="10">
         <v>9</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="10">
-        <v>312.42</v>
+        <v>312.44</v>
       </c>
       <c r="F17" s="10">
-        <v>318.55</v>
+        <v>318.56</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -180,9 +177,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -276,10 +273,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -587,13 +584,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -636,436 +633,406 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>24.476</v>
       </c>
       <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15.175</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15.42</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>15.17512</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>15.41988</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>91080</v>
       </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>48.313</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I3" s="1">
-        <v>1.47</v>
+        <v>71.02</v>
       </c>
       <c r="J3">
-        <v>71.02011</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>72.4695</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3">
+        <v>72.47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>7692</v>
       </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>40.073</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I4" s="1">
-        <v>1.48</v>
+        <v>59.308</v>
       </c>
       <c r="J4">
-        <v>59.30804</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>60.51023</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4">
+        <v>60.51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
         <v>82854</v>
       </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>38.583</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="1">
-        <v>1.48</v>
+        <v>57.103</v>
       </c>
       <c r="J5">
-        <v>57.10284</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>58.26033</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5">
+        <v>58.26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
         <v>335331</v>
       </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>6.471</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="1">
-        <v>1.5</v>
+        <v>9.706</v>
       </c>
       <c r="J6">
-        <v>9.7065</v>
+        <v>1.53</v>
       </c>
       <c r="K6" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L6" s="1">
-        <v>9.90063</v>
-      </c>
-      <c r="M6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6">
+        <v>9.901</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
         <v>335372</v>
       </c>
-      <c r="O6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>18.453</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="1">
-        <v>0.63</v>
+        <v>11.625</v>
       </c>
       <c r="J7">
-        <v>11.62539</v>
+        <v>0.64</v>
       </c>
       <c r="K7" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L7" s="1">
-        <v>11.80992</v>
-      </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7">
+        <v>11.81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>91236</v>
       </c>
-      <c r="O7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46227</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>38.662</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="1">
-        <v>1.51</v>
+        <v>58.38</v>
       </c>
       <c r="J8">
-        <v>58.37962</v>
+        <v>1.54</v>
       </c>
       <c r="K8" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L8" s="1">
-        <v>59.53948</v>
-      </c>
-      <c r="M8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8">
+        <v>59.539</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
         <v>83225</v>
       </c>
-      <c r="O8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46231</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="1">
-        <v>1.53</v>
+        <v>15.3</v>
       </c>
       <c r="J9">
-        <v>15.3</v>
+        <v>1.56</v>
       </c>
       <c r="K9" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L9" s="1">
         <v>15.6</v>
       </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9">
         <v>91449</v>
       </c>
-      <c r="O9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46231</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>23.516</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I10" s="1">
-        <v>0.63</v>
+        <v>14.815</v>
       </c>
       <c r="J10">
-        <v>14.81508</v>
+        <v>0.64</v>
       </c>
       <c r="K10" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L10" s="1">
-        <v>15.05024</v>
-      </c>
-      <c r="M10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10">
+        <v>15.05</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10">
         <v>91449</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1073,69 +1040,69 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="7">
         <v>182.102</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>1.487173</v>
-      </c>
-      <c r="E15" s="7">
-        <v>270.82</v>
-      </c>
-      <c r="F15" s="7">
+        <v>1.487</v>
+      </c>
+      <c r="E15" s="8">
+        <v>270.817</v>
+      </c>
+      <c r="F15" s="8">
         <v>276.28</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="7">
         <v>66.44499999999999</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>0.626316</v>
-      </c>
-      <c r="E16" s="7">
-        <v>41.62</v>
-      </c>
-      <c r="F16" s="7">
+        <v>0.626</v>
+      </c>
+      <c r="E16" s="8">
+        <v>41.615</v>
+      </c>
+      <c r="F16" s="8">
         <v>42.28</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="10">
         <v>248.547</v>
@@ -1145,7 +1112,7 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="10">
-        <v>312.44</v>
+        <v>312.432</v>
       </c>
       <c r="F17" s="10">
         <v>318.56</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,10 +58,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В8987ВР</t>
@@ -85,19 +88,43 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:41</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:18:00</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>15:44:00</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>09:36:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>3236615086 3236615086</t>
+  </si>
+  <si>
+    <t>3236621756 3236621756</t>
+  </si>
+  <si>
+    <t>3236730915 3236730915</t>
+  </si>
+  <si>
+    <t>3236731213 3236731213</t>
+  </si>
+  <si>
+    <t>3236955554 3236955554</t>
+  </si>
+  <si>
+    <t>3236987621 3236987621</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -122,10 +149,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -205,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -219,10 +247,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,16 +556,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,54 +606,60 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>23.062</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>14.76</v>
+        <v>23.82</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
       </c>
       <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>14.99</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
-        <v>91646</v>
+        <v>23.582</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15.721</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
       </c>
       <c r="M2">
-        <v>241684</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>92092</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46238</v>
+        <v>46253</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -631,247 +668,303 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>36.361</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>55.269</v>
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.429</v>
       </c>
       <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>56.36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>83550</v>
+        <v>14.29</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>242117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>92092</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46239</v>
+        <v>46255</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4">
-        <v>46.948</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>71.361</v>
+        <v>15.61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.99</v>
       </c>
       <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>72.76900000000001</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>8236</v>
+        <v>15.454</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="1">
+        <v>10.303</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
       </c>
       <c r="M4">
-        <v>141684</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>92245</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>39.1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I5" s="1">
+        <v>55.874</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K5" s="1">
+        <v>61.387</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>84231</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>45.1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I6" s="1">
+        <v>65.801</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K6" s="1">
+        <v>71.258</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6">
+        <v>8755</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>23.424</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5">
-        <v>15.226</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>25.27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I7" s="1">
+        <v>25.017</v>
+      </c>
+      <c r="J7" s="1">
         <v>0.66</v>
       </c>
-      <c r="J5">
-        <v>15.46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>91839</v>
-      </c>
-      <c r="M5">
-        <v>245027</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="K7" s="1">
+        <v>16.678</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>92432</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="7">
+        <v>94.2</v>
+      </c>
+      <c r="C12" s="8">
+        <v>3</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.44337</v>
+      </c>
+      <c r="E12" s="7">
+        <v>135.96</v>
+      </c>
+      <c r="F12" s="7">
+        <v>148.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F6">
-        <v>36.232</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H6">
-        <v>55.073</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J6">
-        <v>56.16</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6">
-        <v>83836</v>
-      </c>
-      <c r="M6">
-        <v>245532</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7">
-        <v>119.541</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B13" s="7">
+        <v>64.7</v>
+      </c>
+      <c r="C13" s="8">
         <v>3</v>
       </c>
-      <c r="D11" s="8">
-        <v>1.52001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>181.7</v>
-      </c>
-      <c r="F11" s="7">
-        <v>185.289</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="7">
-        <v>46.486</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.64505</v>
-      </c>
-      <c r="E12" s="7">
-        <v>29.99</v>
-      </c>
-      <c r="F12" s="7">
-        <v>30.45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="10">
-        <v>166.027</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>211.69</v>
-      </c>
-      <c r="F13" s="10">
-        <v>215.739</v>
+      <c r="D13" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E13" s="7">
+        <v>64.05</v>
+      </c>
+      <c r="F13" s="7">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="11">
+        <v>158.9</v>
+      </c>
+      <c r="C14" s="12">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="11">
+        <v>200.01</v>
+      </c>
+      <c r="F14" s="11">
+        <v>190.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -633,10 +633,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>23.582</v>
+        <v>15.483</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -677,10 +677,10 @@
         <v>24</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>14.29</v>
+        <v>15.3</v>
       </c>
       <c r="J3" s="1">
         <v>1.56</v>
@@ -721,10 +721,10 @@
         <v>24</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>15.454</v>
+        <v>10.146</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -765,10 +765,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I5" s="1">
-        <v>55.874</v>
+        <v>60.214</v>
       </c>
       <c r="J5" s="1">
         <v>1.57</v>
@@ -809,10 +809,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I6" s="1">
-        <v>65.801</v>
+        <v>69.905</v>
       </c>
       <c r="J6" s="1">
         <v>1.58</v>
@@ -853,10 +853,10 @@
         <v>24</v>
       </c>
       <c r="H7" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="1">
-        <v>25.017</v>
+        <v>16.426</v>
       </c>
       <c r="J7" s="1">
         <v>0.66</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="9">
-        <v>1.44337</v>
+        <v>1.54373</v>
       </c>
       <c r="E12" s="7">
-        <v>135.96</v>
+        <v>145.42</v>
       </c>
       <c r="F12" s="7">
         <v>148.24</v>
@@ -935,10 +935,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E13" s="7">
-        <v>64.05</v>
+        <v>42.06</v>
       </c>
       <c r="F13" s="7">
         <v>42.7</v>
@@ -956,7 +956,7 @@
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="11">
-        <v>200.01</v>
+        <v>187.48</v>
       </c>
       <c r="F14" s="11">
         <v>190.94</v>
